--- a/docs/签到表.xlsx
+++ b/docs/签到表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\A_Senior\C_软件工程实践\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E952D69-91C4-453E-875C-90CC6C0A6348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6937BE9C-E99C-4A06-A0D2-E364F05D37BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11870" yWindow="2640" windowWidth="11930" windowHeight="12640" xr2:uid="{052747DC-6BAE-464D-9B40-33BBC39E1DCC}"/>
   </bookViews>
@@ -551,7 +551,9 @@
       <c r="D3" s="2">
         <v>1</v>
       </c>
-      <c r="E3" s="2"/>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
